--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486965_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486965_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8043</v>
+        <v>4.2791</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1415</v>
+        <v>2.5504</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6628</v>
+        <v>1.7288</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4778</v>
+        <v>4.8661</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9831</v>
+        <v>1.943</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4947</v>
+        <v>2.9231</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7792</v>
+        <v>4.1076</v>
       </c>
       <c r="K2" t="n">
-        <v>2.424</v>
+        <v>2.1607</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3552</v>
+        <v>1.9469</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3014</v>
+        <v>0.7585</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4409</v>
+        <v>-0.2177</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1395</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2321</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2588</v>
+        <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9014</v>
+        <v>-0.3467</v>
       </c>
       <c r="T2" t="n">
-        <v>3.196</v>
+        <v>-0.3333</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2946</v>
+        <v>-0.0134</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.2402</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.8070000000000001</v>
+        <v>0.8295</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9094</v>
+        <v>3.4734</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3306</v>
+        <v>1.8402</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5788</v>
+        <v>1.6331</v>
       </c>
       <c r="G3" t="n">
-        <v>1.208</v>
+        <v>2.4778</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2914</v>
+        <v>0.9831</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4994</v>
+        <v>1.4947</v>
       </c>
       <c r="J3" t="n">
-        <v>1.202</v>
+        <v>2.7792</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6</v>
+        <v>2.424</v>
       </c>
       <c r="L3" t="n">
-        <v>1.802</v>
+        <v>0.3552</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006</v>
+        <v>-0.3014</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6913</v>
+        <v>-1.4409</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6974</v>
+        <v>1.1395</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4374</v>
+        <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2209</v>
+        <v>0.5705</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0931</v>
+        <v>0.8948</v>
       </c>
       <c r="U3" t="n">
-        <v>1.314</v>
+        <v>-0.3243</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0698</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2484</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6968</v>
+        <v>3.4508</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0274</v>
+        <v>2.4352</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6695</v>
+        <v>1.0156</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8661</v>
+        <v>1.208</v>
       </c>
       <c r="H4" t="n">
-        <v>1.943</v>
+        <v>-1.2914</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9231</v>
+        <v>2.4994</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1076</v>
+        <v>1.202</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1607</v>
+        <v>-0.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9469</v>
+        <v>1.802</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7585</v>
+        <v>0.006</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2177</v>
+        <v>-0.6913</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.6974</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0.4107</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.929</v>
+        <v>0.7623</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8563</v>
+        <v>0.0115</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0727</v>
+        <v>0.7508</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2402</v>
+        <v>1.0698</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8295</v>
+        <v>2.2484</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0698</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9956</v>
+        <v>3.428</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4732</v>
+        <v>0.787</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5224</v>
+        <v>2.641</v>
       </c>
       <c r="G5" t="n">
         <v>2.2733</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.75</v>
+        <v>-0.3177</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4534</v>
+        <v>-0.1396</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2967</v>
+        <v>-0.1781</v>
       </c>
       <c r="V5" t="n">
         <v>0.2402</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0681</v>
+        <v>2.9608</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8982</v>
+        <v>1.3166</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1699</v>
+        <v>1.6442</v>
       </c>
       <c r="G6" t="n">
         <v>1.5377</v>
@@ -922,13 +922,13 @@
         <v>2.4641</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6482</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5542</v>
+        <v>-0.1358</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.094</v>
+        <v>-0.6197</v>
       </c>
       <c r="V6" t="n">
         <v>1.7679</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3061</v>
+        <v>2.2458</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0308</v>
+        <v>-2.2986</v>
       </c>
       <c r="F7" t="n">
-        <v>4.3368</v>
+        <v>4.5443</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2744</v>
@@ -1000,13 +1000,13 @@
         <v>2.6694</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2409</v>
+        <v>-0.3012</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1198</v>
+        <v>-0.3876</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1211</v>
+        <v>0.0864</v>
       </c>
       <c r="V7" t="n">
         <v>1.1786</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BONO SOLER</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1484</v>
+        <v>1.4027</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2368</v>
+        <v>1.219</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0883</v>
+        <v>0.1837</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6374</v>
+        <v>2.9272</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3861</v>
+        <v>-1.1585</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0235</v>
+        <v>4.0857</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6634</v>
+        <v>2.7603</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.639</v>
+        <v>-0.5806</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3024</v>
+        <v>3.3408</v>
       </c>
       <c r="M8" t="n">
-        <v>0.974</v>
+        <v>0.1669</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2528</v>
+        <v>-0.578</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7211</v>
+        <v>0.7449</v>
       </c>
       <c r="P8" t="n">
-        <v>0.616</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R8" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3139</v>
+        <v>-0.5327</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5733</v>
+        <v>0.12</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2594</v>
+        <v>-0.6526</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4189</v>
+        <v>0.2402</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9255</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0289</v>
+        <v>1.7151</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1035</v>
+        <v>-1.0442</v>
       </c>
       <c r="G9" t="n">
         <v>3.5536</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3185</v>
+        <v>0.0639</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5075</v>
+        <v>0.1937</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.189</v>
+        <v>-0.1297</v>
       </c>
       <c r="V9" t="n">
         <v>-2.9466</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>P. BONO SOLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6251</v>
+        <v>0.6428</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3821</v>
+        <v>1.0275</v>
       </c>
       <c r="F10" t="n">
-        <v>0.243</v>
+        <v>-0.3847</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9272</v>
+        <v>1.6374</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1585</v>
+        <v>-0.3861</v>
       </c>
       <c r="I10" t="n">
-        <v>4.0857</v>
+        <v>2.0235</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7603</v>
+        <v>0.6634</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5806</v>
+        <v>-0.639</v>
       </c>
       <c r="L10" t="n">
-        <v>3.3408</v>
+        <v>1.3024</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1669</v>
+        <v>0.974</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.578</v>
+        <v>0.2528</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7449</v>
+        <v>0.7211</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3102</v>
+        <v>-0.1917</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7169</v>
+        <v>0.3641</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5933</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2402</v>
+        <v>-1.4189</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3439</v>
+        <v>-0.4485</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3647</v>
+        <v>-2.4693</v>
       </c>
       <c r="F11" t="n">
         <v>2.0208</v>
@@ -1312,10 +1312,10 @@
         <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6315</v>
+        <v>-0.7361</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1122</v>
+        <v>0.0076</v>
       </c>
       <c r="U11" t="n">
         <v>-0.7437</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7547</v>
+        <v>-0.725</v>
       </c>
       <c r="E12" t="n">
         <v>0.3935</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1482</v>
+        <v>-1.1185</v>
       </c>
       <c r="G12" t="n">
         <v>1.1683</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0461</v>
+        <v>-0.0165</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0856</v>
+        <v>0.1153</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8768</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.3807</v>
+        <v>21.3808</v>
       </c>
       <c r="E13" t="n">
-        <v>8.516699999999997</v>
+        <v>8.516599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>12.864</v>
+        <v>12.8641</v>
       </c>
       <c r="G13" t="n">
         <v>21.5641</v>
@@ -1468,10 +1468,10 @@
         <v>17.4541</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8012</v>
+        <v>-1.8014</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4636000000000001</v>
+        <v>0.4637000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-2.2649</v>
@@ -1480,7 +1480,7 @@
         <v>-0.4354999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>8.318</v>
+        <v>8.318000000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-8.753400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2872</v>
+        <v>2.9776</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9463</v>
+        <v>2.2601</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3409</v>
+        <v>0.7175</v>
       </c>
       <c r="G14" t="n">
         <v>-1.1188</v>
@@ -1546,13 +1546,13 @@
         <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7718</v>
+        <v>-0.0814</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1939</v>
+        <v>0.1199</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5779</v>
+        <v>-0.2013</v>
       </c>
       <c r="V14" t="n">
         <v>3.7671</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1032</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0099</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.1438</v>
       </c>
       <c r="G15" t="n">
         <v>-2.1462</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6396</v>
+        <v>0.461</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9877</v>
+        <v>0.0463</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6519</v>
+        <v>0.4147</v>
       </c>
       <c r="V15" t="n">
         <v>2.2259</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ROKER</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1075</v>
+        <v>-0.5734</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1136</v>
+        <v>-0.2229</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0061</v>
+        <v>-0.3505</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1896</v>
+        <v>-1.8042</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7887</v>
+        <v>-1.0544</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9783</v>
+        <v>-0.7498</v>
       </c>
       <c r="J16" t="n">
-        <v>0.77</v>
+        <v>-1.2968</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7305</v>
+        <v>-0.639</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>-0.6579</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9596</v>
+        <v>-0.5074</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0582</v>
+        <v>-0.4154</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0177</v>
+        <v>-0.092</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.4374</v>
+        <v>-1.2321</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3572</v>
+        <v>0.5192</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5538</v>
+        <v>0.8871</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8034</v>
+        <v>-0.368</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4805</v>
+        <v>0.7117</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4805</v>
+        <v>-0.7072000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>E. COLL COMABELLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1898</v>
+        <v>-0.6896</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3001</v>
+        <v>-0.4891</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.49</v>
+        <v>-0.2004</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8042</v>
+        <v>0.3536</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0544</v>
+        <v>0.3536</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7498</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2968</v>
+        <v>0.6034</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.639</v>
+        <v>0.6034</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6579</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5074</v>
+        <v>-0.2498</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4154</v>
+        <v>-0.2498</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.092</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-1.2321</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.2321</v>
-      </c>
       <c r="S17" t="n">
-        <v>0.9026999999999999</v>
+        <v>-0.0165</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4102</v>
+        <v>-0.0659</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5075</v>
+        <v>0.0494</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7117</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7072000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. COLL COMABELLA</t>
+          <t>A. ROKER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7192</v>
+        <v>-0.9253</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4891</v>
+        <v>-0.4274</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2301</v>
+        <v>-0.4978</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3536</v>
+        <v>-1.1896</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3536</v>
+        <v>0.7887</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-1.9783</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6034</v>
+        <v>0.77</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6034</v>
+        <v>0.7305</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0395</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2498</v>
+        <v>-1.9596</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2498</v>
+        <v>0.0582</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-2.0177</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-1.4374</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0461</v>
+        <v>0.5395</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0659</v>
+        <v>0.24</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0198</v>
+        <v>0.2995</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9891</v>
+        <v>-1.6421</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0446</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9445</v>
+        <v>-1.5975</v>
       </c>
       <c r="G19" t="n">
         <v>-2.753</v>
@@ -1936,13 +1936,13 @@
         <v>2.4641</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2414</v>
+        <v>0.1055</v>
       </c>
       <c r="T19" t="n">
         <v>0.4957</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7371</v>
+        <v>-0.3902</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2267</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7366</v>
+        <v>-2.5519</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1351</v>
+        <v>-2.0305</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6015</v>
+        <v>-0.5213</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1135</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2976</v>
+        <v>0.4824</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1858</v>
+        <v>0.2904</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1117</v>
+        <v>0.1919</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5367</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6031</v>
+        <v>-3.0661</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.5357</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.649</v>
+        <v>-2.5304</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0312</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.537</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.527</v>
+        <v>-0.1086</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.01</v>
+        <v>0.1086</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4189</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.8831</v>
+        <v>-6.0567</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.212</v>
+        <v>-4.5844</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6711</v>
+        <v>-1.4723</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5301</v>
@@ -2170,13 +2170,13 @@
         <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5842000000000001</v>
+        <v>0.2421</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3062</v>
+        <v>0.3214</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.278</v>
+        <v>-0.0793</v>
       </c>
       <c r="V22" t="n">
         <v>-2.126</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.5426</v>
+        <v>-8.0806</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.1717</v>
+        <v>-6.8578</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3709</v>
+        <v>-1.2227</v>
       </c>
       <c r="G23" t="n">
         <v>-7.231</v>
@@ -2248,13 +2248,13 @@
         <v>1.8481</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2151</v>
+        <v>0.2469</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2753</v>
+        <v>0.0385</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0602</v>
+        <v>0.2084</v>
       </c>
       <c r="V23" t="n">
         <v>-0.4805</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-21.3806</v>
+        <v>-20.6835</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.8639</v>
+        <v>-12.8638</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.5168</v>
+        <v>-7.819199999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-21.564</v>
@@ -2311,7 +2311,7 @@
         <v>-15.1358</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.311199999999999</v>
+        <v>-3.3112</v>
       </c>
       <c r="O24" t="n">
         <v>-11.8243</v>
@@ -2326,16 +2326,16 @@
         <v>15.4005</v>
       </c>
       <c r="S24" t="n">
-        <v>1.8015</v>
+        <v>2.4987</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2649</v>
+        <v>2.2648</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4634999999999999</v>
+        <v>0.2337</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4354000000000006</v>
+        <v>0.4354000000000011</v>
       </c>
       <c r="W24" t="n">
         <v>8.753399999999999</v>
